--- a/data/trans_dic/IP1006-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1006-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen cardiopatía congénita</t>
+          <t>Menores que padecen cardiopatía congénita (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,44</t>
+          <t>0,0; 6,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,01</t>
+          <t>0,0; 7,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 5,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,58</t>
+          <t>0,42; 3,91</t>
         </is>
       </c>
     </row>
@@ -787,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -797,22 +798,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,12</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,32</t>
+          <t>0,09; 1,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,65</t>
+          <t>0,37; 1,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,88</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,15</t>
+          <t>0,28; 1,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,84</t>
+          <t>0,07; 0,75</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,36</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,94</t>
+          <t>0,1; 0,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,67</t>
+          <t>0,0; 0,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,98</t>
+          <t>0,09; 0,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,87</t>
+          <t>0,09; 0,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,47</t>
+          <t>0,36; 1,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,82</t>
+          <t>0,08; 0,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,65</t>
+          <t>0,13; 0,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,96</t>
+          <t>0,24; 0,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,63</t>
+          <t>0,13; 0,65</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen cardiopatía congénita (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1769</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4314</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3612</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5883</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3722</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4624</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6814</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>539; 5001</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4066</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1366</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2761</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5412</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2902</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4491</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4767</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5366</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>409; 5609</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1805; 8126</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4790</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>694; 6926</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2602; 10764</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>666; 7246</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2645</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3364</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3140</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4266</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2510</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1346</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2673</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4610</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7234</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4672</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>661; 5946</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4089</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>604; 6238</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>685; 5664</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2679; 11495</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>624; 5261</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1880; 9683</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3470; 14109</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1938; 9470</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1006-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1006-Estudios-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,75</t>
+          <t>0,0; 5,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,08</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,04</t>
+          <t>0,0; 8,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,42</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,91</t>
+          <t>0,41; 3,73</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,08</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,37 +798,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,18</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,65</t>
+          <t>0,3; 1,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,78</t>
+          <t>0,08; 0,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,14</t>
+          <t>0,28; 1,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,75</t>
+          <t>0,07; 0,71</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,87</t>
+          <t>0,09; 0,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,58</t>
+          <t>0,0; 0,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,89</t>
+          <t>0,09; 0,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,78</t>
+          <t>0,09; 0,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,54</t>
+          <t>0,37; 1,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,71</t>
+          <t>0,08; 0,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,69</t>
+          <t>0,13; 0,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,97</t>
+          <t>0,23; 0,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,65</t>
+          <t>0,14; 0,66</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4314</t>
+          <t>0; 4673</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3612</t>
+          <t>0; 3721</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1326,27 +1326,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5883</t>
+          <t>0; 6730</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3722</t>
+          <t>0; 2623</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4624</t>
+          <t>0; 4122</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6814</t>
+          <t>0; 7882</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>539; 5001</t>
+          <t>529; 4777</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4491</t>
+          <t>0; 3336</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4767</t>
+          <t>0; 4759</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5366</t>
+          <t>0; 5018</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>409; 5609</t>
+          <t>0; 5611</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1805; 8126</t>
+          <t>1456; 8616</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4790</t>
+          <t>0; 4328</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>694; 6926</t>
+          <t>696; 6239</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2602; 10764</t>
+          <t>2652; 10427</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>666; 7246</t>
+          <t>665; 6827</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2645</t>
+          <t>0; 2643</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3364</t>
+          <t>0; 3865</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3140</t>
+          <t>0; 2120</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4266</t>
+          <t>0; 3362</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>661; 5946</t>
+          <t>642; 5675</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4089</t>
+          <t>0; 4709</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>604; 6238</t>
+          <t>658; 6757</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>685; 5664</t>
+          <t>686; 6321</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2679; 11495</t>
+          <t>2751; 11600</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>624; 5261</t>
+          <t>626; 5491</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1880; 9683</t>
+          <t>1892; 8727</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3470; 14109</t>
+          <t>3319; 12384</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1938; 9470</t>
+          <t>2001; 9605</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1006-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1006-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,91%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,01</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,4</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,27</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,06</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 6,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,73</t>
+          <t>0,42; 3,58</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,14; 1,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0,28; 1,65</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,88</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,86</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,06</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,06</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,18</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,3; 1,75</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,7</t>
+          <t>0,08; 0,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,11</t>
+          <t>0,23; 1,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,71</t>
+          <t>0,09; 0,84</t>
         </is>
       </c>
     </row>
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,37 +898,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,94</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,51</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,25</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,83</t>
+          <t>0,09; 0,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,33; 1,47</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,08; 0,82</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,1; 0,94</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,67</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,96</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,88</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 1,55</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,74</t>
+          <t>0,09; 0,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,62</t>
+          <t>0,14; 0,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,85</t>
+          <t>0,27; 0,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,66</t>
+          <t>0,13; 0,63</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1325</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1136</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1155</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4673</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 6689</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3500</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3995</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3721</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 6730</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2623</t>
+          <t>0; 3826</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4122</t>
+          <t>0; 4239</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 7882</t>
+          <t>0; 5418</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>529; 4777</t>
+          <t>534; 4586</t>
         </is>
       </c>
     </row>
@@ -1363,27 +1363,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4066</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1366</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>661</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1346</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1537</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4066</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1366</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3336</t>
+          <t>685; 6318</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4759</t>
+          <t>1361; 8147</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5018</t>
+          <t>0; 4301</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 5611</t>
+          <t>0; 3572</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1456; 8616</t>
+          <t>0; 4755</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4328</t>
+          <t>0; 5269</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>696; 6239</t>
+          <t>695; 6994</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2652; 10427</t>
+          <t>2171; 10830</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>665; 6827</t>
+          <t>870; 8115</t>
         </is>
       </c>
     </row>
@@ -1526,27 +1526,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1579,27 +1579,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1632,42 +1632,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2643</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0; 3328</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2630</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3865</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2120</t>
+          <t>0; 2619</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3362</t>
+          <t>0; 3376</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5889</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2510</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1346</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2673</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2100</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>642; 5675</t>
+          <t>684; 6292</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4709</t>
+          <t>2503; 10983</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>658; 6757</t>
+          <t>627; 6071</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>686; 6321</t>
+          <t>665; 6411</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2751; 11600</t>
+          <t>0; 4746</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>626; 5491</t>
+          <t>602; 6913</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1892; 8727</t>
+          <t>1976; 9081</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3319; 12384</t>
+          <t>3863; 13895</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2001; 9605</t>
+          <t>1880; 9152</t>
         </is>
       </c>
     </row>
